--- a/database/danhmuc.xlsx
+++ b/database/danhmuc.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC50FB-A4E6-41DA-A647-5C88E36E0964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4CD11C-25DC-466B-A25B-78C38F960995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
+    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
   </bookViews>
   <sheets>
     <sheet name="ScrapDetails" sheetId="1" r:id="rId1"/>
     <sheet name="tbl_RQ_MaterialIssueB" sheetId="5" r:id="rId2"/>
-    <sheet name="Scraps" sheetId="2" r:id="rId3"/>
-    <sheet name="MaterNametemplate" sheetId="3" r:id="rId4"/>
-    <sheet name="tbl_MV_Master_ACC" sheetId="4" r:id="rId5"/>
+    <sheet name="MaterNametemplate2" sheetId="6" r:id="rId3"/>
+    <sheet name="Scraps" sheetId="2" r:id="rId4"/>
+    <sheet name="MaterNametemplate" sheetId="3" r:id="rId5"/>
+    <sheet name="tbl_MV_Master_ACC" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4940" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5032" uniqueCount="328">
   <si>
     <t>Id</t>
   </si>
@@ -869,6 +870,162 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>AccountCost</t>
+  </si>
+  <si>
+    <t>1.Other Issue Materials</t>
+  </si>
+  <si>
+    <t>Xuất/Nhập NVL cho mục đích như Gửi hàng mẫu, làm JIG, check ROSH, phân tích, check Assembly,…</t>
+  </si>
+  <si>
+    <t>2.Return Materials</t>
+  </si>
+  <si>
+    <t>3.Material Shortage</t>
+  </si>
+  <si>
+    <t>4.Claim Scrap Material</t>
+  </si>
+  <si>
+    <t>4.1.Claim Scrap Material (Claim transportation company)</t>
+  </si>
+  <si>
+    <t>Hàng mua từ vendor nhưng NG do bên vận chuyển, đòi tiền bên vận chuyển</t>
+  </si>
+  <si>
+    <t>5.Disposition</t>
+  </si>
+  <si>
+    <t>Hàng NVL hủy do PSNV chịu chi phí</t>
+  </si>
+  <si>
+    <t>6.Claim Scrap Halb</t>
+  </si>
+  <si>
+    <t>7.Claim Scrap Deadstock</t>
+  </si>
+  <si>
+    <t>Hàng NVL mua của 1 vendor và không dùng nữa vendor khác chịu chi phí và hủy tại PSNV</t>
+  </si>
+  <si>
+    <t>8.Issue for lending</t>
+  </si>
+  <si>
+    <t>Xuất HALB cho vendor, sau đó, hàng trả về PSNV và đòi tiền vendor theo Claim scrap half (hợp đồng Lending và General Sanction)</t>
+  </si>
+  <si>
+    <t>9.Sale Deadstock</t>
+  </si>
+  <si>
+    <t>àng NVL mua của 1 vendor và không dùng nữa nên xuất bán cho 1 vendor khác</t>
+  </si>
+  <si>
+    <t>10.Compensation</t>
+  </si>
+  <si>
+    <t>Hàng NVL mua về nhưng không dùng do sai thiết kế, vendor chịu chi phí, hủy tại PSNV</t>
+  </si>
+  <si>
+    <t>11.Outsourcing</t>
+  </si>
+  <si>
+    <t>Hàng NVL issue out dùng cho outsourcing</t>
+  </si>
+  <si>
+    <t>12.Claim Insurance</t>
+  </si>
+  <si>
+    <t>Hàng NVL bị hỏng trong quá trình vận chuyển và được bồi thường bảo hiểm</t>
+  </si>
+  <si>
+    <t>13.1 Issue Out For Rework (Issue Debitnote)</t>
+  </si>
+  <si>
+    <t>13.2 Issue Out For Rework (Issue Debitnote)</t>
+  </si>
+  <si>
+    <t>13.3 Issue Out For Rework (Not issue Debit Note)</t>
+  </si>
+  <si>
+    <t>13.4 Issue Out For Rework (Not issue Debit Note)</t>
+  </si>
+  <si>
+    <t>14.Issue Sub-Materials</t>
+  </si>
+  <si>
+    <t>Issue NVL phụ cho tiêu dùng nội bộ</t>
+  </si>
+  <si>
+    <t>15.Post Difference End Of Month</t>
+  </si>
+  <si>
+    <t>Post difference giữa tồn kho thực tế và hệ thống</t>
+  </si>
+  <si>
+    <t>16.Post Difference Outsourcing</t>
+  </si>
+  <si>
+    <t>Post difference giữa tồn kho thực tế và hệ thống của kho nhà thầu phụ</t>
+  </si>
+  <si>
+    <t>17.Production Rejects</t>
+  </si>
+  <si>
+    <t>Hàng hỏng do sản xuất</t>
+  </si>
+  <si>
+    <t>18.Production Rejects for Outsourcing</t>
+  </si>
+  <si>
+    <t>Hàng hỏng do sản xuất của kho nhà thầu phụ</t>
+  </si>
+  <si>
+    <t>19.Issue For Investigation</t>
+  </si>
+  <si>
+    <t>Gửi hàng NVL cho vendor để phân tích không issue debit note</t>
+  </si>
+  <si>
+    <t>20.Other Issue</t>
+  </si>
+  <si>
+    <t>Xuất bù cho việc xuất nhầm hàng cho customers…</t>
+  </si>
+  <si>
+    <t>21.Claim investigation halb</t>
+  </si>
+  <si>
+    <t>Claim vendor cho hàng halb gửi cho khách hàng kiểm tra do vendor thay đổi NVL, NVL mua của vendor bị NG làm hỏng cả hàng Halb của PSNV sau đó gửi cả hàng halb cho vendor phân tích và issue debit note đòi tiền cho tất cả hàng Halb đó</t>
+  </si>
+  <si>
+    <t>22.Issue Sub-Materials</t>
+  </si>
+  <si>
+    <t>Issue hàng sub materials cho Headphone IPC</t>
+  </si>
+  <si>
+    <t>23.Scrap mixing part</t>
+  </si>
+  <si>
+    <t>Scrap mixing part</t>
+  </si>
+  <si>
+    <t>23.Scrap mixing part (For Outsourcing)</t>
+  </si>
+  <si>
+    <t>Scrap mixing part (For Outsourcing)</t>
+  </si>
+  <si>
+    <t>24.Issue Sub-material (Export processing)</t>
+  </si>
+  <si>
+    <t>Hàng sub dùng cho SXXK</t>
   </si>
 </sst>
 </file>
@@ -20181,6 +20338,535 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F148C9-9463-4E78-B0E7-C2CB47A49A7B}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="215.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>6210211000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4">
+        <v>6210140000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5">
+        <v>6210300000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6">
+        <v>6210140000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7">
+        <v>6210140000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E8">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>6210110000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E10">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" t="s">
+        <v>291</v>
+      </c>
+      <c r="E11">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" t="s">
+        <v>293</v>
+      </c>
+      <c r="E12">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D13" t="s">
+        <v>295</v>
+      </c>
+      <c r="E13">
+        <v>6210300000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>296</v>
+      </c>
+      <c r="D14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E14">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>298</v>
+      </c>
+      <c r="D15" t="s">
+        <v>299</v>
+      </c>
+      <c r="E15">
+        <v>6210160000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>301</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" t="s">
+        <v>305</v>
+      </c>
+      <c r="E20">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E21">
+        <v>6210211000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>308</v>
+      </c>
+      <c r="D22" t="s">
+        <v>309</v>
+      </c>
+      <c r="E22">
+        <v>6210210000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D23" t="s">
+        <v>311</v>
+      </c>
+      <c r="E23">
+        <v>6210020000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24">
+        <v>6210020000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>314</v>
+      </c>
+      <c r="D25" t="s">
+        <v>315</v>
+      </c>
+      <c r="E25">
+        <v>6210130000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" t="s">
+        <v>317</v>
+      </c>
+      <c r="E26">
+        <v>6210130000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>318</v>
+      </c>
+      <c r="D27" t="s">
+        <v>319</v>
+      </c>
+      <c r="E27">
+        <v>6210300000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" t="s">
+        <v>321</v>
+      </c>
+      <c r="E28">
+        <v>6418000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>322</v>
+      </c>
+      <c r="D29" t="s">
+        <v>323</v>
+      </c>
+      <c r="E29">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>324</v>
+      </c>
+      <c r="D30" t="s">
+        <v>325</v>
+      </c>
+      <c r="E30">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>326</v>
+      </c>
+      <c r="D31" t="s">
+        <v>327</v>
+      </c>
+      <c r="E31">
+        <v>6210131000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB2A697-C446-42CA-9EA3-E6C04F2B3C6B}">
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20628,7 +21314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E11ED9-094A-4E34-902C-E4D83A2AC484}">
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20846,7 +21532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617C8F75-5E10-424B-9C5C-5796BD725456}">
   <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/database/danhmuc.xlsx
+++ b/database/danhmuc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\scminnovation\SCM_Inovation\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4CD11C-25DC-466B-A25B-78C38F960995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7377DFB-E6CD-4D51-A0F0-1EA4B832F37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
   </bookViews>
   <sheets>
     <sheet name="ScrapDetails" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="MaterNametemplate" sheetId="3" r:id="rId5"/>
     <sheet name="tbl_MV_Master_ACC" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1380,9 +1380,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA16E188-59D3-44EF-906A-9F4A097652A4}">
   <dimension ref="A1:AN66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2779</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2780</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2781</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2782</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2783</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2784</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2785</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2786</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2787</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2788</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2789</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2790</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2791</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2792</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2793</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2794</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2795</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2796</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2797</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2798</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2799</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2800</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2801</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2802</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2803</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2804</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2805</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2806</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2807</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2808</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2809</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2810</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2811</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2812</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2813</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2814</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2815</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2816</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2817</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2818</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2819</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2820</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2821</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2822</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2823</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2824</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2825</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2826</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2827</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2828</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2829</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2830</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2831</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2832</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2833</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2834</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2835</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2836</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2837</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2838</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2839</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2840</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2841</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2842</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2843</v>
       </c>
@@ -7492,9 +7492,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014F1AF3-9B63-42AF-B62F-90B5F4FD19C3}">
   <dimension ref="A1:BQ65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>139</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1270</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1269</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1203</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1202</v>
       </c>
@@ -8503,7 +8503,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1201</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1200</v>
       </c>
@@ -8897,7 +8897,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1199</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1198</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1197</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1196</v>
       </c>
@@ -9685,7 +9685,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1195</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1194</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1193</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1192</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1191</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1190</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1189</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1188</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1187</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1186</v>
       </c>
@@ -11655,7 +11655,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1185</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1184</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1183</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1182</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1181</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1180</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1179</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1178</v>
       </c>
@@ -13231,7 +13231,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1177</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1176</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1175</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1174</v>
       </c>
@@ -14019,7 +14019,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1173</v>
       </c>
@@ -14216,7 +14216,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1172</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1171</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1170</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1169</v>
       </c>
@@ -15004,7 +15004,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1168</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1167</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1166</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1165</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1164</v>
       </c>
@@ -15989,7 +15989,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1163</v>
       </c>
@@ -16186,7 +16186,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1162</v>
       </c>
@@ -16383,7 +16383,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1161</v>
       </c>
@@ -16580,7 +16580,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1160</v>
       </c>
@@ -16777,7 +16777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1159</v>
       </c>
@@ -16974,7 +16974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1158</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1157</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1156</v>
       </c>
@@ -17565,7 +17565,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1155</v>
       </c>
@@ -17762,7 +17762,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1154</v>
       </c>
@@ -17959,7 +17959,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1153</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1152</v>
       </c>
@@ -18353,7 +18353,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="56" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1151</v>
       </c>
@@ -18550,7 +18550,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1150</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1149</v>
       </c>
@@ -18944,7 +18944,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="59" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1148</v>
       </c>
@@ -19141,7 +19141,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>1147</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>1146</v>
       </c>
@@ -19535,7 +19535,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1145</v>
       </c>
@@ -19732,7 +19732,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>1144</v>
       </c>
@@ -19929,7 +19929,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>1143</v>
       </c>
@@ -20126,7 +20126,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1010</v>
       </c>
@@ -20339,17 +20339,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F148C9-9463-4E78-B0E7-C2CB47A49A7B}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="215.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.54296875" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>135</v>
       </c>
@@ -20366,7 +20366,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -20379,47 +20379,62 @@
       <c r="D2" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>6210211000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>138</v>
+      </c>
       <c r="B3">
-        <v>6210211000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>6210140000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>138</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D4" t="s">
         <v>44</v>
       </c>
       <c r="E4">
-        <v>6210140000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6210300000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>138</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
       </c>
       <c r="E5">
-        <v>6210300000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6210140000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -20427,169 +20442,169 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>284</v>
       </c>
       <c r="E6">
         <v>6210140000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E7">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>138</v>
       </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D7" t="s">
-        <v>284</v>
-      </c>
-      <c r="E7">
-        <v>6210140000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>137</v>
-      </c>
       <c r="B8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D8" t="s">
-        <v>286</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>8110110000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6210110000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>138</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>289</v>
       </c>
       <c r="E9">
-        <v>6210110000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E10">
         <v>8110110000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E11">
         <v>8110110000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>138</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E12">
+        <v>6210300000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D13" t="s">
+        <v>297</v>
+      </c>
+      <c r="E13">
         <v>8110110000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>294</v>
-      </c>
-      <c r="D13" t="s">
-        <v>295</v>
-      </c>
-      <c r="E13">
-        <v>6210300000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D14" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14">
+        <v>6210160000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>137</v>
       </c>
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>296</v>
-      </c>
-      <c r="D14" t="s">
-        <v>297</v>
-      </c>
-      <c r="E14">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15">
         <v>8110110000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>298</v>
-      </c>
-      <c r="D15" t="s">
-        <v>299</v>
-      </c>
-      <c r="E15">
-        <v>6210160000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>137</v>
       </c>
@@ -20597,7 +20612,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D16" t="s">
         <v>44</v>
@@ -20606,7 +20621,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>137</v>
       </c>
@@ -20614,7 +20629,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -20623,7 +20638,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>137</v>
       </c>
@@ -20631,7 +20646,7 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -20640,224 +20655,207 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>137</v>
       </c>
       <c r="B19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="E19">
         <v>8110110000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>137</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E20">
-        <v>8110110000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6210211000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D21" t="s">
+        <v>309</v>
+      </c>
+      <c r="E21">
+        <v>6210210000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>137</v>
       </c>
-      <c r="B21">
-        <v>15</v>
-      </c>
-      <c r="C21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E21">
-        <v>6210211000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>310</v>
+      </c>
+      <c r="D22" t="s">
+        <v>311</v>
+      </c>
+      <c r="E22">
+        <v>6210020000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>138</v>
       </c>
-      <c r="B22">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>308</v>
-      </c>
-      <c r="D22" t="s">
-        <v>309</v>
-      </c>
-      <c r="E22">
-        <v>6210210000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>137</v>
-      </c>
       <c r="B23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D23" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E23">
         <v>6210020000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>138</v>
       </c>
       <c r="B24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E24">
-        <v>6210020000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6210130000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E25">
         <v>6210130000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>318</v>
+      </c>
+      <c r="D26" t="s">
+        <v>319</v>
+      </c>
+      <c r="E26">
+        <v>6210300000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>137</v>
       </c>
-      <c r="B26">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>316</v>
-      </c>
-      <c r="D26" t="s">
-        <v>317</v>
-      </c>
-      <c r="E26">
-        <v>6210130000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>138</v>
-      </c>
       <c r="B27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D27" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E27">
-        <v>6210300000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6418000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>137</v>
       </c>
       <c r="B28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E28">
-        <v>6418000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8110110000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29">
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E29">
         <v>8110110000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D30" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E30">
-        <v>8110110000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>137</v>
-      </c>
-      <c r="B31">
-        <v>24</v>
-      </c>
-      <c r="C31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D31" t="s">
-        <v>327</v>
-      </c>
-      <c r="E31">
         <v>6210131000</v>
       </c>
     </row>
@@ -20869,9 +20867,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB2A697-C446-42CA-9EA3-E6C04F2B3C6B}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -20909,7 +20907,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -20947,7 +20945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -20985,7 +20983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>4</v>
       </c>
@@ -21023,7 +21021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
@@ -21061,7 +21059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7</v>
       </c>
@@ -21099,7 +21097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>8</v>
       </c>
@@ -21131,7 +21129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>9</v>
       </c>
@@ -21163,7 +21161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>22</v>
       </c>
@@ -21201,7 +21199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>30</v>
       </c>
@@ -21239,7 +21237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>31</v>
       </c>
@@ -21271,7 +21269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>32</v>
       </c>
@@ -21317,9 +21315,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E11ED9-094A-4E34-902C-E4D83A2AC484}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>135</v>
       </c>
@@ -21327,7 +21325,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -21335,7 +21333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>137</v>
       </c>
@@ -21343,7 +21341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>137</v>
       </c>
@@ -21351,7 +21349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>137</v>
       </c>
@@ -21359,7 +21357,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -21367,7 +21365,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -21375,7 +21373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -21383,7 +21381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -21391,7 +21389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -21399,7 +21397,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>137</v>
       </c>
@@ -21407,7 +21405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -21415,7 +21413,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -21423,7 +21421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -21431,7 +21429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -21439,7 +21437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>138</v>
       </c>
@@ -21447,7 +21445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>138</v>
       </c>
@@ -21455,7 +21453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>138</v>
       </c>
@@ -21463,7 +21461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>138</v>
       </c>
@@ -21471,7 +21469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>138</v>
       </c>
@@ -21479,7 +21477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>138</v>
       </c>
@@ -21487,7 +21485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -21495,7 +21493,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -21503,7 +21501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -21511,7 +21509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>138</v>
       </c>
@@ -21519,7 +21517,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -21535,9 +21533,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617C8F75-5E10-424B-9C5C-5796BD725456}">
   <dimension ref="A1:J52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>139</v>
       </c>
@@ -21569,7 +21567,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2</v>
       </c>
@@ -21598,7 +21596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -21627,7 +21625,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>4</v>
       </c>
@@ -21656,7 +21654,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
@@ -21685,7 +21683,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>6</v>
       </c>
@@ -21714,7 +21712,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7</v>
       </c>
@@ -21743,7 +21741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>8</v>
       </c>
@@ -21772,7 +21770,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>9</v>
       </c>
@@ -21801,7 +21799,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>10</v>
       </c>
@@ -21830,7 +21828,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>11</v>
       </c>
@@ -21859,7 +21857,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>12</v>
       </c>
@@ -21888,7 +21886,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>13</v>
       </c>
@@ -21917,7 +21915,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>14</v>
       </c>
@@ -21946,7 +21944,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>15</v>
       </c>
@@ -21975,7 +21973,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>16</v>
       </c>
@@ -22004,7 +22002,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>17</v>
       </c>
@@ -22033,7 +22031,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>18</v>
       </c>
@@ -22062,7 +22060,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>19</v>
       </c>
@@ -22091,7 +22089,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>20</v>
       </c>
@@ -22120,7 +22118,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>21</v>
       </c>
@@ -22149,7 +22147,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>22</v>
       </c>
@@ -22178,7 +22176,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>23</v>
       </c>
@@ -22207,7 +22205,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>24</v>
       </c>
@@ -22236,7 +22234,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>25</v>
       </c>
@@ -22265,7 +22263,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>26</v>
       </c>
@@ -22294,7 +22292,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>27</v>
       </c>
@@ -22323,7 +22321,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>28</v>
       </c>
@@ -22352,7 +22350,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>29</v>
       </c>
@@ -22381,7 +22379,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>30</v>
       </c>
@@ -22410,7 +22408,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>31</v>
       </c>
@@ -22439,7 +22437,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>32</v>
       </c>
@@ -22468,7 +22466,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>33</v>
       </c>
@@ -22497,7 +22495,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>34</v>
       </c>
@@ -22526,7 +22524,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>35</v>
       </c>
@@ -22555,7 +22553,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>36</v>
       </c>
@@ -22584,7 +22582,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>37</v>
       </c>
@@ -22613,7 +22611,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>38</v>
       </c>
@@ -22642,7 +22640,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>39</v>
       </c>
@@ -22671,7 +22669,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>40</v>
       </c>
@@ -22700,7 +22698,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>41</v>
       </c>
@@ -22729,7 +22727,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>42</v>
       </c>
@@ -22758,7 +22756,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>43</v>
       </c>
@@ -22787,7 +22785,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>44</v>
       </c>
@@ -22816,7 +22814,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>45</v>
       </c>
@@ -22845,7 +22843,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>46</v>
       </c>
@@ -22874,7 +22872,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>47</v>
       </c>
@@ -22903,7 +22901,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>48</v>
       </c>
@@ -22932,7 +22930,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>49</v>
       </c>
@@ -22961,7 +22959,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>50</v>
       </c>
@@ -22990,7 +22988,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>51</v>
       </c>
@@ -23022,7 +23020,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>52</v>
       </c>

--- a/database/danhmuc.xlsx
+++ b/database/danhmuc.xlsx
@@ -5,20 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\scminnovation\SCM_Inovation\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7377DFB-E6CD-4D51-A0F0-1EA4B832F37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB91663-3B9F-4C6D-8F56-E6DB7D750147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
+    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
   </bookViews>
   <sheets>
     <sheet name="ScrapDetails" sheetId="1" r:id="rId1"/>
     <sheet name="tbl_RQ_MaterialIssueB" sheetId="5" r:id="rId2"/>
     <sheet name="MaterNametemplate2" sheetId="6" r:id="rId3"/>
-    <sheet name="Scraps" sheetId="2" r:id="rId4"/>
-    <sheet name="MaterNametemplate" sheetId="3" r:id="rId5"/>
-    <sheet name="tbl_MV_Master_ACC" sheetId="4" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId4"/>
+    <sheet name="Scraps" sheetId="2" r:id="rId5"/>
+    <sheet name="MaterNametemplate" sheetId="3" r:id="rId6"/>
+    <sheet name="tbl_MV_Master_ACC" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5032" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="338">
   <si>
     <t>Id</t>
   </si>
@@ -1026,6 +1027,36 @@
   </si>
   <si>
     <t>Hàng sub dùng cho SXXK</t>
+  </si>
+  <si>
+    <t>Request_NO</t>
+  </si>
+  <si>
+    <t>QtyIssue</t>
+  </si>
+  <si>
+    <t>giacu</t>
+  </si>
+  <si>
+    <t>amountcu</t>
+  </si>
+  <si>
+    <t>giamoi</t>
+  </si>
+  <si>
+    <t>amountmoi</t>
+  </si>
+  <si>
+    <t>UserID</t>
+  </si>
+  <si>
+    <t>CreateDate</t>
+  </si>
+  <si>
+    <t>2007600_ACC</t>
+  </si>
+  <si>
+    <t>FROM [Issue_MaterialInOut].[dbo].[tbl_History_change_price_SAP] order by CreateDate desc</t>
   </si>
 </sst>
 </file>
@@ -1380,9 +1411,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA16E188-59D3-44EF-906A-9F4A097652A4}">
   <dimension ref="A1:AN66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1535,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2779</v>
       </c>
@@ -1596,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2780</v>
       </c>
@@ -1688,7 +1719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2781</v>
       </c>
@@ -1780,7 +1811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2782</v>
       </c>
@@ -1872,7 +1903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2783</v>
       </c>
@@ -1964,7 +1995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2784</v>
       </c>
@@ -2056,7 +2087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2785</v>
       </c>
@@ -2148,7 +2179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2786</v>
       </c>
@@ -2240,7 +2271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2787</v>
       </c>
@@ -2332,7 +2363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2788</v>
       </c>
@@ -2424,7 +2455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2789</v>
       </c>
@@ -2516,7 +2547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2790</v>
       </c>
@@ -2608,7 +2639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2791</v>
       </c>
@@ -2700,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2792</v>
       </c>
@@ -2792,7 +2823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2793</v>
       </c>
@@ -2884,7 +2915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2794</v>
       </c>
@@ -2976,7 +3007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2795</v>
       </c>
@@ -3068,7 +3099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2796</v>
       </c>
@@ -3160,7 +3191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2797</v>
       </c>
@@ -3252,7 +3283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2798</v>
       </c>
@@ -3344,7 +3375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2799</v>
       </c>
@@ -3436,7 +3467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2800</v>
       </c>
@@ -3528,7 +3559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2801</v>
       </c>
@@ -3620,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2802</v>
       </c>
@@ -3712,7 +3743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2803</v>
       </c>
@@ -3804,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2804</v>
       </c>
@@ -3896,7 +3927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2805</v>
       </c>
@@ -3988,7 +4019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2806</v>
       </c>
@@ -4080,7 +4111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2807</v>
       </c>
@@ -4172,7 +4203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2808</v>
       </c>
@@ -4264,7 +4295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2809</v>
       </c>
@@ -4356,7 +4387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2810</v>
       </c>
@@ -4448,7 +4479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2811</v>
       </c>
@@ -4540,7 +4571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2812</v>
       </c>
@@ -4632,7 +4663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2813</v>
       </c>
@@ -4724,7 +4755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2814</v>
       </c>
@@ -4816,7 +4847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2815</v>
       </c>
@@ -4908,7 +4939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2816</v>
       </c>
@@ -5000,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2817</v>
       </c>
@@ -5092,7 +5123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2818</v>
       </c>
@@ -5184,7 +5215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2819</v>
       </c>
@@ -5276,7 +5307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2820</v>
       </c>
@@ -5368,7 +5399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2821</v>
       </c>
@@ -5460,7 +5491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2822</v>
       </c>
@@ -5552,7 +5583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2823</v>
       </c>
@@ -5644,7 +5675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2824</v>
       </c>
@@ -5736,7 +5767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2825</v>
       </c>
@@ -5828,7 +5859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2826</v>
       </c>
@@ -5920,7 +5951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2827</v>
       </c>
@@ -6012,7 +6043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2828</v>
       </c>
@@ -6104,7 +6135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2829</v>
       </c>
@@ -6196,7 +6227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2830</v>
       </c>
@@ -6288,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2831</v>
       </c>
@@ -6380,7 +6411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2832</v>
       </c>
@@ -6472,7 +6503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2833</v>
       </c>
@@ -6564,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2834</v>
       </c>
@@ -6656,7 +6687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2835</v>
       </c>
@@ -6748,7 +6779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2836</v>
       </c>
@@ -6840,7 +6871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2837</v>
       </c>
@@ -6932,7 +6963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2838</v>
       </c>
@@ -7024,7 +7055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2839</v>
       </c>
@@ -7116,7 +7147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2840</v>
       </c>
@@ -7208,7 +7239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2841</v>
       </c>
@@ -7300,7 +7331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2842</v>
       </c>
@@ -7392,7 +7423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2843</v>
       </c>
@@ -7492,9 +7523,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014F1AF3-9B63-42AF-B62F-90B5F4FD19C3}">
   <dimension ref="A1:BQ65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>139</v>
       </c>
@@ -7703,7 +7734,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1270</v>
       </c>
@@ -7906,7 +7937,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1269</v>
       </c>
@@ -8109,7 +8140,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1203</v>
       </c>
@@ -8306,7 +8337,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1202</v>
       </c>
@@ -8503,7 +8534,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1201</v>
       </c>
@@ -8700,7 +8731,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1200</v>
       </c>
@@ -8897,7 +8928,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1199</v>
       </c>
@@ -9094,7 +9125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1198</v>
       </c>
@@ -9291,7 +9322,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1197</v>
       </c>
@@ -9488,7 +9519,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1196</v>
       </c>
@@ -9685,7 +9716,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1195</v>
       </c>
@@ -9882,7 +9913,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1194</v>
       </c>
@@ -10079,7 +10110,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1193</v>
       </c>
@@ -10276,7 +10307,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1192</v>
       </c>
@@ -10473,7 +10504,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1191</v>
       </c>
@@ -10670,7 +10701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1190</v>
       </c>
@@ -10867,7 +10898,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1189</v>
       </c>
@@ -11064,7 +11095,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1188</v>
       </c>
@@ -11261,7 +11292,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1187</v>
       </c>
@@ -11458,7 +11489,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1186</v>
       </c>
@@ -11655,7 +11686,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1185</v>
       </c>
@@ -11852,7 +11883,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1184</v>
       </c>
@@ -12049,7 +12080,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1183</v>
       </c>
@@ -12246,7 +12277,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1182</v>
       </c>
@@ -12443,7 +12474,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1181</v>
       </c>
@@ -12640,7 +12671,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1180</v>
       </c>
@@ -12837,7 +12868,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1179</v>
       </c>
@@ -13034,7 +13065,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1178</v>
       </c>
@@ -13231,7 +13262,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1177</v>
       </c>
@@ -13428,7 +13459,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1176</v>
       </c>
@@ -13625,7 +13656,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1175</v>
       </c>
@@ -13822,7 +13853,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1174</v>
       </c>
@@ -14019,7 +14050,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1173</v>
       </c>
@@ -14216,7 +14247,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1172</v>
       </c>
@@ -14413,7 +14444,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1171</v>
       </c>
@@ -14610,7 +14641,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1170</v>
       </c>
@@ -14807,7 +14838,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1169</v>
       </c>
@@ -15004,7 +15035,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1168</v>
       </c>
@@ -15201,7 +15232,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1167</v>
       </c>
@@ -15398,7 +15429,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1166</v>
       </c>
@@ -15595,7 +15626,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1165</v>
       </c>
@@ -15792,7 +15823,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1164</v>
       </c>
@@ -15989,7 +16020,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1163</v>
       </c>
@@ -16186,7 +16217,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1162</v>
       </c>
@@ -16383,7 +16414,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1161</v>
       </c>
@@ -16580,7 +16611,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1160</v>
       </c>
@@ -16777,7 +16808,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1159</v>
       </c>
@@ -16974,7 +17005,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1158</v>
       </c>
@@ -17171,7 +17202,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1157</v>
       </c>
@@ -17368,7 +17399,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1156</v>
       </c>
@@ -17565,7 +17596,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1155</v>
       </c>
@@ -17762,7 +17793,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1154</v>
       </c>
@@ -17959,7 +17990,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1153</v>
       </c>
@@ -18156,7 +18187,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1152</v>
       </c>
@@ -18353,7 +18384,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="56" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1151</v>
       </c>
@@ -18550,7 +18581,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1150</v>
       </c>
@@ -18747,7 +18778,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1149</v>
       </c>
@@ -18944,7 +18975,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="59" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1148</v>
       </c>
@@ -19141,7 +19172,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1147</v>
       </c>
@@ -19338,7 +19369,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1146</v>
       </c>
@@ -19535,7 +19566,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1145</v>
       </c>
@@ -19732,7 +19763,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1144</v>
       </c>
@@ -19929,7 +19960,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1143</v>
       </c>
@@ -20126,7 +20157,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1010</v>
       </c>
@@ -20340,16 +20371,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F148C9-9463-4E78-B0E7-C2CB47A49A7B}">
   <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.54296875" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>135</v>
       </c>
@@ -20366,7 +20397,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -20383,7 +20414,7 @@
         <v>6210211000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -20400,7 +20431,7 @@
         <v>6210140000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -20417,7 +20448,7 @@
         <v>6210300000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -20434,7 +20465,7 @@
         <v>6210140000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -20451,7 +20482,7 @@
         <v>6210140000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -20468,7 +20499,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -20485,7 +20516,7 @@
         <v>6210110000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>138</v>
       </c>
@@ -20502,7 +20533,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -20519,7 +20550,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -20536,7 +20567,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -20553,7 +20584,7 @@
         <v>6210300000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -20570,7 +20601,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -20587,7 +20618,7 @@
         <v>6210160000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>137</v>
       </c>
@@ -20604,7 +20635,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>137</v>
       </c>
@@ -20621,7 +20652,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>137</v>
       </c>
@@ -20638,7 +20669,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>137</v>
       </c>
@@ -20655,7 +20686,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>137</v>
       </c>
@@ -20672,7 +20703,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>137</v>
       </c>
@@ -20689,7 +20720,7 @@
         <v>6210211000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>138</v>
       </c>
@@ -20706,7 +20737,7 @@
         <v>6210210000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>137</v>
       </c>
@@ -20723,7 +20754,7 @@
         <v>6210020000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -20740,7 +20771,7 @@
         <v>6210020000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -20757,7 +20788,7 @@
         <v>6210130000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -20774,7 +20805,7 @@
         <v>6210130000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -20791,7 +20822,7 @@
         <v>6210300000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -20808,7 +20839,7 @@
         <v>6418000000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>137</v>
       </c>
@@ -20825,7 +20856,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>138</v>
       </c>
@@ -20842,7 +20873,7 @@
         <v>8110110000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -20865,446 +20896,328 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB2A697-C446-42CA-9EA3-E6C04F2B3C6B}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE28473-EFB2-425B-94E1-E634CF0DB181}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>328</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>329</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>330</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>331</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>332</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>333</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="K1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>201</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="2">
-        <v>45755</v>
-      </c>
-      <c r="G2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="1">
-        <v>45882.4479790162</v>
-      </c>
-      <c r="I2" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>2000</v>
+      </c>
+      <c r="G2">
+        <v>10000</v>
+      </c>
+      <c r="H2">
+        <v>3000</v>
+      </c>
+      <c r="I2">
+        <v>15000</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46010.600093287037</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>555</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="2">
-        <v>45756</v>
-      </c>
-      <c r="G3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="1">
-        <v>45908.645348923608</v>
-      </c>
-      <c r="I3" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2000</v>
+      </c>
+      <c r="G3">
+        <v>10000</v>
+      </c>
+      <c r="H3">
+        <v>3000</v>
+      </c>
+      <c r="I3">
+        <v>15000</v>
       </c>
       <c r="J3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K3" s="1">
+        <v>46010.600074618058</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>555</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="2">
-        <v>45756</v>
-      </c>
-      <c r="G4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" s="1">
-        <v>45908.646385844906</v>
-      </c>
-      <c r="I4" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1000</v>
+      </c>
+      <c r="G4">
+        <v>5000</v>
+      </c>
+      <c r="H4">
+        <v>2000</v>
+      </c>
+      <c r="I4">
+        <v>10000</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K4" s="1">
+        <v>46009.6999659375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>555</v>
-      </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="2">
-        <v>45756</v>
-      </c>
-      <c r="G5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="1">
-        <v>45908.71085289352</v>
-      </c>
-      <c r="I5" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
+        <v>5000</v>
+      </c>
+      <c r="H5">
+        <v>2000</v>
+      </c>
+      <c r="I5">
+        <v>10000</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K5" s="1">
+        <v>46009.699960069447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>201</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="2">
-        <v>45756</v>
-      </c>
-      <c r="G6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="1">
-        <v>45910.657659108794</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5000</v>
+      </c>
+      <c r="G6">
+        <v>25000</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <v>5000</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K6" s="1">
+        <v>46009.699159872682</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H7" s="1">
-        <v>45918.684193831017</v>
-      </c>
-      <c r="I7" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>3000</v>
+      </c>
+      <c r="G7">
+        <v>15000</v>
+      </c>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <v>5000</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K7" s="1">
+        <v>46009.699106863423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>45925</v>
-      </c>
-      <c r="G8" t="s">
-        <v>129</v>
-      </c>
-      <c r="H8" s="1">
-        <v>45925.568801817128</v>
-      </c>
-      <c r="I8" t="s">
-        <v>44</v>
+        <v>262</v>
+      </c>
+      <c r="C8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>10000</v>
+      </c>
+      <c r="G8">
+        <v>50000</v>
+      </c>
+      <c r="H8">
+        <v>5000</v>
+      </c>
+      <c r="I8">
+        <v>25000</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="K8" s="1">
+        <v>46009.694944756942</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
+        <v>262</v>
+      </c>
+      <c r="C9" t="s">
+        <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="E9">
-        <v>201</v>
-      </c>
-      <c r="F9" s="2">
-        <v>45964</v>
-      </c>
-      <c r="G9" t="s">
-        <v>129</v>
-      </c>
-      <c r="H9" s="1">
-        <v>45964.654340277775</v>
-      </c>
-      <c r="I9" t="s">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>10000</v>
+      </c>
+      <c r="G9">
+        <v>50000</v>
+      </c>
+      <c r="H9">
+        <v>3000</v>
+      </c>
+      <c r="I9">
+        <v>15000</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10">
-        <v>201</v>
-      </c>
-      <c r="F10" s="2">
-        <v>45980</v>
-      </c>
-      <c r="G10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H10" s="1">
-        <v>45980.646025497685</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>45988</v>
-      </c>
-      <c r="G11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H11" s="1">
-        <v>45988.398611458331</v>
-      </c>
-      <c r="I11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12">
-        <v>201</v>
-      </c>
-      <c r="F12" s="2">
-        <v>45992</v>
-      </c>
-      <c r="G12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H12" s="1">
-        <v>45992.574803819443</v>
-      </c>
-      <c r="I12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+        <v>336</v>
+      </c>
+      <c r="K9" s="1">
+        <v>46009.694903391202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -21313,216 +21226,446 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E11ED9-094A-4E34-902C-E4D83A2AC484}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB2A697-C446-42CA-9EA3-E6C04F2B3C6B}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4">
+      <c r="B2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>201</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2">
+        <v>45755</v>
+      </c>
+      <c r="G2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="1">
+        <v>45882.4479790162</v>
+      </c>
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>555</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45756</v>
+      </c>
+      <c r="G3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="1">
+        <v>45908.645348923608</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>555</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="2">
+        <v>45756</v>
+      </c>
+      <c r="G4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45908.646385844906</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>555</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45756</v>
+      </c>
+      <c r="G5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="1">
+        <v>45908.71085289352</v>
+      </c>
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>201</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2">
+        <v>45756</v>
+      </c>
+      <c r="G6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="1">
+        <v>45910.657659108794</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H7" s="1">
+        <v>45918.684193831017</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11">
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>45925</v>
+      </c>
+      <c r="G8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" s="1">
+        <v>45925.568801817128</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B26">
-        <v>23</v>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>201</v>
+      </c>
+      <c r="F9" s="2">
+        <v>45964</v>
+      </c>
+      <c r="G9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="1">
+        <v>45964.654340277775</v>
+      </c>
+      <c r="I9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10">
+        <v>201</v>
+      </c>
+      <c r="F10" s="2">
+        <v>45980</v>
+      </c>
+      <c r="G10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="1">
+        <v>45980.646025497685</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>45988</v>
+      </c>
+      <c r="G11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="1">
+        <v>45988.398611458331</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12">
+        <v>201</v>
+      </c>
+      <c r="F12" s="2">
+        <v>45992</v>
+      </c>
+      <c r="G12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="1">
+        <v>45992.574803819443</v>
+      </c>
+      <c r="I12" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21531,11 +21674,229 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E11ED9-094A-4E34-902C-E4D83A2AC484}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617C8F75-5E10-424B-9C5C-5796BD725456}">
   <dimension ref="A1:J52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>139</v>
       </c>
@@ -21567,7 +21928,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -21596,7 +21957,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -21625,7 +21986,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -21654,7 +22015,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -21683,7 +22044,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -21712,7 +22073,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -21741,7 +22102,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -21770,7 +22131,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -21799,7 +22160,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -21828,7 +22189,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -21857,7 +22218,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -21886,7 +22247,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -21915,7 +22276,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -21944,7 +22305,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -21973,7 +22334,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -22002,7 +22363,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -22031,7 +22392,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -22060,7 +22421,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -22089,7 +22450,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -22118,7 +22479,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -22147,7 +22508,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -22176,7 +22537,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
@@ -22205,7 +22566,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
@@ -22234,7 +22595,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -22263,7 +22624,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
@@ -22292,7 +22653,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
@@ -22321,7 +22682,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>28</v>
       </c>
@@ -22350,7 +22711,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>29</v>
       </c>
@@ -22379,7 +22740,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>30</v>
       </c>
@@ -22408,7 +22769,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>31</v>
       </c>
@@ -22437,7 +22798,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>32</v>
       </c>
@@ -22466,7 +22827,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>33</v>
       </c>
@@ -22495,7 +22856,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>34</v>
       </c>
@@ -22524,7 +22885,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>35</v>
       </c>
@@ -22553,7 +22914,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>36</v>
       </c>
@@ -22582,7 +22943,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>37</v>
       </c>
@@ -22611,7 +22972,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>38</v>
       </c>
@@ -22640,7 +23001,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>39</v>
       </c>
@@ -22669,7 +23030,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>40</v>
       </c>
@@ -22698,7 +23059,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>41</v>
       </c>
@@ -22727,7 +23088,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>42</v>
       </c>
@@ -22756,7 +23117,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>43</v>
       </c>
@@ -22785,7 +23146,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>44</v>
       </c>
@@ -22814,7 +23175,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>45</v>
       </c>
@@ -22843,7 +23204,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>46</v>
       </c>
@@ -22872,7 +23233,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>47</v>
       </c>
@@ -22901,7 +23262,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>48</v>
       </c>
@@ -22930,7 +23291,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>49</v>
       </c>
@@ -22959,7 +23320,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>50</v>
       </c>
@@ -22988,7 +23349,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>51</v>
       </c>
@@ -23020,7 +23381,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>52</v>
       </c>
